--- a/assets/excel/account_file_info.xlsx
+++ b/assets/excel/account_file_info.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>开户文件编号</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t>文件版本</t>
+  </si>
+  <si>
+    <t>文件路径</t>
   </si>
   <si>
     <t>签署状态</t>
@@ -553,7 +556,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1241,14 +1244,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="7"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="6" width="16.7211538461538" customWidth="1"/>
-    <col min="7" max="8" width="17.9423076923077" customWidth="1"/>
+    <col min="1" max="7" width="16.7211538461538" customWidth="1"/>
+    <col min="8" max="9" width="17.9423076923077" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1273,6 +1276,9 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" ht="14" customHeight="1"/>
     <row r="3" ht="14" customHeight="1"/>

--- a/assets/excel/account_file_info.xlsx
+++ b/assets/excel/account_file_info.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>开户文件编号</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>使用模板</t>
+  </si>
+  <si>
+    <t>模板编码</t>
   </si>
   <si>
     <t>客户经理编号</t>
@@ -1244,14 +1247,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="7" width="16.7211538461538" customWidth="1"/>
-    <col min="8" max="9" width="17.9423076923077" customWidth="1"/>
+    <col min="8" max="10" width="17.9423076923077" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1279,6 +1282,9 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" ht="14" customHeight="1"/>
     <row r="3" ht="14" customHeight="1"/>

--- a/assets/excel/account_file_info.xlsx
+++ b/assets/excel/account_file_info.xlsx
@@ -47,7 +47,7 @@
     <t>签署状态</t>
   </si>
   <si>
-    <t>开户方式</t>
+    <t>文件类型</t>
   </si>
   <si>
     <t>使用模板</t>
